--- a/static/data/exports/Retro_HP_GE_2024.xlsx
+++ b/static/data/exports/Retro_HP_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>53</v>
@@ -1027,26 +1027,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1506084</v>
+        <v>1506085</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bhuvnesh Kumar</t>
+          <t>Dev Raj Bhardwaj</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>RTSMJD</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16549</v>
+        <v>16550</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0447943765828782</v>
+        <v>0.04</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Bhuvnesh Kumar</t>
+          <t>Dev Raj Bhardwaj</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>RTSMJD</t>
         </is>
       </c>
       <c r="Q10" t="b">
@@ -1089,26 +1089,26 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1506086</v>
+        <v>1506084</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Narain Singh Dogra</t>
+          <t>Bhuvnesh Kumar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HCHLJP</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16551</v>
+        <v>16549</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04</v>
+        <v>0.0447943765828782</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Narain Singh Dogra</t>
+          <t>Bhuvnesh Kumar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>HCHLJP</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="Q11" t="b">
@@ -1151,20 +1151,20 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1506085</v>
+        <v>1506086</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dev Raj Bhardwaj</t>
+          <t>Narain Singh Dogra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RTSMJD</t>
+          <t>HCHLJP</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16550</v>
+        <v>16551</v>
       </c>
       <c r="E12" t="n">
         <v>26</v>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dev Raj Bhardwaj</t>
+          <t>Narain Singh Dogra</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RTSMJD</t>
+          <t>HCHLJP</t>
         </is>
       </c>
       <c r="Q12" t="b">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>53</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>53</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="Q35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>53</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>53</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>53</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>53</v>
@@ -5181,26 +5181,26 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1506435</v>
+        <v>1506434</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bhuvnesh Kumar</t>
+          <t>Achal Singh</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>16549</v>
+        <v>16536</v>
       </c>
       <c r="E77" t="n">
         <v>21</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03</v>
+        <v>0.0323669487215055</v>
       </c>
       <c r="G77" t="n">
         <v>10</v>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Bhuvnesh Kumar</t>
+          <t>Achal Singh</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q77" t="b">
@@ -5243,26 +5243,26 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1506434</v>
+        <v>1506435</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Achal Singh</t>
+          <t>Bhuvnesh Kumar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16536</v>
+        <v>16549</v>
       </c>
       <c r="E78" t="n">
         <v>21</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0323669487215055</v>
+        <v>0.03</v>
       </c>
       <c r="G78" t="n">
         <v>10</v>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Achal Singh</t>
+          <t>Bhuvnesh Kumar</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="Q78" t="b">
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>53</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>53</v>
@@ -7661,26 +7661,26 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1506681</v>
+        <v>1506680</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Surender Kumar Gautam</t>
+          <t>Hem Raj</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>16536</v>
+        <v>16537</v>
       </c>
       <c r="E117" t="n">
         <v>92</v>
       </c>
       <c r="F117" t="n">
-        <v>0.17</v>
+        <v>0.168180904155165</v>
       </c>
       <c r="G117" t="n">
         <v>4</v>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Surender Kumar Gautam</t>
+          <t>Hem Raj</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="Q117" t="b">
@@ -7723,26 +7723,26 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1506680</v>
+        <v>1506681</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hem Raj</t>
+          <t>Surender Kumar Gautam</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>16537</v>
+        <v>16536</v>
       </c>
       <c r="E118" t="n">
         <v>92</v>
       </c>
       <c r="F118" t="n">
-        <v>0.168180904155165</v>
+        <v>0.17</v>
       </c>
       <c r="G118" t="n">
         <v>4</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Hem Raj</t>
+          <t>Surender Kumar Gautam</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q118" t="b">
@@ -8033,26 +8033,26 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1506687</v>
+        <v>1506686</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jagdeep Kumar</t>
+          <t>Arun Ankesh Syal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>ESBD</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>16549</v>
+        <v>16569</v>
       </c>
       <c r="E123" t="n">
         <v>20</v>
       </c>
       <c r="F123" t="n">
-        <v>0.04</v>
+        <v>0.036561066120688</v>
       </c>
       <c r="G123" t="n">
         <v>10</v>
@@ -8070,12 +8070,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Jagdeep Kumar</t>
+          <t>Arun Ankesh Syal</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>RTRYDVBHMP</t>
+          <t>ESBD</t>
         </is>
       </c>
       <c r="Q123" t="b">
@@ -8095,26 +8095,26 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1506686</v>
+        <v>1506687</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Arun Ankesh Syal</t>
+          <t>Jagdeep Kumar</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ESBD</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>16569</v>
+        <v>16549</v>
       </c>
       <c r="E124" t="n">
         <v>20</v>
       </c>
       <c r="F124" t="n">
-        <v>0.036561066120688</v>
+        <v>0.04</v>
       </c>
       <c r="G124" t="n">
         <v>10</v>
@@ -8132,12 +8132,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Arun Ankesh Syal</t>
+          <t>Jagdeep Kumar</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>ESBD</t>
+          <t>RTRYDVBHMP</t>
         </is>
       </c>
       <c r="Q124" t="b">
@@ -8157,11 +8157,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1506689</v>
+        <v>1506688</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Gopi Chand Attari</t>
+          <t>Garib Dass Katoch</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8176,7 +8176,7 @@
         <v>5</v>
       </c>
       <c r="F125" t="n">
-        <v>0.01</v>
+        <v>0.00914026653017201</v>
       </c>
       <c r="G125" t="n">
         <v>12</v>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Gopi Chand Attari</t>
+          <t>Garib Dass Katoch</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8219,11 +8219,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1506688</v>
+        <v>1506689</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Garib Dass Katoch</t>
+          <t>Gopi Chand Attari</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8238,7 +8238,7 @@
         <v>5</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00914026653017201</v>
+        <v>0.01</v>
       </c>
       <c r="G126" t="n">
         <v>12</v>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Garib Dass Katoch</t>
+          <t>Gopi Chand Attari</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="Q127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>53</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="Q138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>53</v>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="Q149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>53</v>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="Q160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>53</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="Q171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>53</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="Q182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>53</v>
@@ -12419,7 +12419,7 @@
         </is>
       </c>
       <c r="Q193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>53</v>
@@ -13101,7 +13101,7 @@
         </is>
       </c>
       <c r="Q204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>53</v>
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="Q215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>53</v>
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="Q227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>53</v>
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="Q237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
         <v>53</v>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="Q248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>53</v>
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="Q259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
         <v>53</v>
@@ -16899,26 +16899,26 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1507499</v>
+        <v>1507498</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Vinay Kumar</t>
+          <t>Mahesh Saini</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>HCHLJP</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>16548</v>
+        <v>16551</v>
       </c>
       <c r="E266" t="n">
         <v>24</v>
       </c>
       <c r="F266" t="n">
-        <v>0.04</v>
+        <v>0.0423086415400345</v>
       </c>
       <c r="G266" t="n">
         <v>8</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Vinay Kumar</t>
+          <t>Mahesh Saini</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>HCHLJP</t>
         </is>
       </c>
       <c r="Q266" t="b">
@@ -16961,26 +16961,26 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1507498</v>
+        <v>1507499</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Mahesh Saini</t>
+          <t>Vinay Kumar</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>HCHLJP</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>16551</v>
+        <v>16548</v>
       </c>
       <c r="E267" t="n">
         <v>24</v>
       </c>
       <c r="F267" t="n">
-        <v>0.0423086415400345</v>
+        <v>0.04</v>
       </c>
       <c r="G267" t="n">
         <v>8</v>
@@ -16998,12 +16998,12 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Mahesh Saini</t>
+          <t>Vinay Kumar</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>HCHLJP</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="Q267" t="b">
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="Q271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
         <v>53</v>
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="Q281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>53</v>
@@ -18557,7 +18557,7 @@
         </is>
       </c>
       <c r="Q292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>53</v>
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="Q303" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R303" t="n">
         <v>53</v>
@@ -19921,7 +19921,7 @@
         </is>
       </c>
       <c r="Q314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R314" t="n">
         <v>53</v>
@@ -19999,26 +19999,26 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1507801</v>
+        <v>1507802</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Dr. Prakash Chand Bhardwaj</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>16537</v>
+        <v>16540</v>
       </c>
       <c r="E316" t="n">
         <v>291</v>
       </c>
       <c r="F316" t="n">
-        <v>0.427972645047429</v>
+        <v>0.43</v>
       </c>
       <c r="G316" t="n">
         <v>3</v>
@@ -20036,12 +20036,12 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Dr. Prakash Chand Bhardwaj</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q316" t="b">
@@ -20061,26 +20061,26 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1507802</v>
+        <v>1507801</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Dr. Prakash Chand Bhardwaj</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>16540</v>
+        <v>16537</v>
       </c>
       <c r="E317" t="n">
         <v>291</v>
       </c>
       <c r="F317" t="n">
-        <v>0.43</v>
+        <v>0.427972645047429</v>
       </c>
       <c r="G317" t="n">
         <v>3</v>
@@ -20098,12 +20098,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Dr. Prakash Chand Bhardwaj</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="Q317" t="b">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="Q325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R325" t="n">
         <v>53</v>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="Q336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R336" t="n">
         <v>53</v>
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="Q360" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R360" t="n">
         <v>53</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="Q371" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R371" t="n">
         <v>53</v>
@@ -24137,7 +24137,7 @@
         </is>
       </c>
       <c r="Q382" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R382" t="n">
         <v>53</v>
@@ -31593,26 +31593,26 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1508722</v>
+        <v>1508721</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Sumit Rana</t>
+          <t>Subedar Major Kulwant Singh Patial</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>BHRJWNKP</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>16548</v>
+        <v>16568</v>
       </c>
       <c r="E503" t="n">
         <v>44</v>
       </c>
       <c r="F503" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0673235816145418</v>
       </c>
       <c r="G503" t="n">
         <v>7</v>
@@ -31630,12 +31630,12 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Sumit Rana</t>
+          <t>Subedar Major Kulwant Singh Patial</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>BHRJWNKP</t>
         </is>
       </c>
       <c r="Q503" t="b">
@@ -31655,26 +31655,26 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1508721</v>
+        <v>1508722</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Subedar Major Kulwant Singh Patial</t>
+          <t>Sumit Rana</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>BHRJWNKP</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>16568</v>
+        <v>16548</v>
       </c>
       <c r="E504" t="n">
         <v>44</v>
       </c>
       <c r="F504" t="n">
-        <v>0.0673235816145418</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G504" t="n">
         <v>7</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Subedar Major Kulwant Singh Patial</t>
+          <t>Sumit Rana</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>BHRJWNKP</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="Q504" t="b">
@@ -32709,11 +32709,11 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1508789</v>
+        <v>1508790</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Garib Dass Katoch</t>
+          <t>Gopi Chand Attari</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32728,7 +32728,7 @@
         <v>6</v>
       </c>
       <c r="F521" t="n">
-        <v>0.00883132175448925</v>
+        <v>0.01</v>
       </c>
       <c r="G521" t="n">
         <v>12</v>
@@ -32746,7 +32746,7 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Garib Dass Katoch</t>
+          <t>Gopi Chand Attari</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -32771,11 +32771,11 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1508790</v>
+        <v>1508789</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Gopi Chand Attari</t>
+          <t>Garib Dass Katoch</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32790,7 +32790,7 @@
         <v>6</v>
       </c>
       <c r="F522" t="n">
-        <v>0.01</v>
+        <v>0.00883132175448925</v>
       </c>
       <c r="G522" t="n">
         <v>12</v>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Gopi Chand Attari</t>
+          <t>Garib Dass Katoch</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -42117,7 +42117,7 @@
         </is>
       </c>
       <c r="Q672" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R672" t="n">
         <v>53</v>
@@ -43171,7 +43171,7 @@
         </is>
       </c>
       <c r="Q689" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R689" t="n">
         <v>53</v>
